--- a/output/roomself_excel/11365.xlsx
+++ b/output/roomself_excel/11365.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>104429</v>
+        <v>90480</v>
       </c>
       <c r="D2" t="n">
-        <v>2616</v>
+        <v>2468</v>
       </c>
       <c r="E2" t="n">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F2" t="n">
-        <v>336</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>297580</v>
+        <v>141375</v>
       </c>
       <c r="D3" t="n">
-        <v>5068</v>
+        <v>3008</v>
       </c>
       <c r="E3" t="n">
-        <v>827</v>
+        <v>375</v>
       </c>
       <c r="F3" t="n">
-        <v>639</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100233</v>
+        <v>104429</v>
       </c>
       <c r="D4" t="n">
-        <v>2584</v>
+        <v>2616</v>
       </c>
       <c r="E4" t="n">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="F4" t="n">
-        <v>283</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42635</v>
+        <v>100233</v>
       </c>
       <c r="D5" t="n">
-        <v>2036</v>
+        <v>2584</v>
       </c>
       <c r="E5" t="n">
-        <v>123</v>
+        <v>446</v>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +554,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>42635</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E6" t="n">
+        <v>109</v>
+      </c>
+      <c r="F6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>65725</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2056</v>
+      </c>
+      <c r="E7" t="n">
+        <v>299</v>
+      </c>
+      <c r="F7" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>17129</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" t="n">
         <v>1092</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E8" t="n">
         <v>133</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>24</v>
       </c>
     </row>

--- a/output/roomself_excel/11365.xlsx
+++ b/output/roomself_excel/11365.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2468</v>
       </c>
-      <c r="E2" t="n">
-        <v>417</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>264</v>
+        <v>240</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>376</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3008</v>
       </c>
-      <c r="E3" t="n">
-        <v>375</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
+        <v>199</v>
+      </c>
+      <c r="G3" t="n">
         <v>56</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>154</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2616</v>
       </c>
-      <c r="E4" t="n">
-        <v>433</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>336</v>
+        <v>277</v>
+      </c>
+      <c r="G4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>377</v>
+      </c>
+      <c r="J4" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2584</v>
       </c>
-      <c r="E5" t="n">
-        <v>446</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>283</v>
+        <v>259</v>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>387</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +647,20 @@
       <c r="D6" t="n">
         <v>2036</v>
       </c>
-      <c r="E6" t="n">
-        <v>109</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>106</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +677,27 @@
       <c r="D7" t="n">
         <v>2056</v>
       </c>
-      <c r="E7" t="n">
-        <v>299</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>263</v>
+        <v>275</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>239</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +715,20 @@
       <c r="D8" t="n">
         <v>1092</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>133</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>24</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
